--- a/SMP-Template.xlsx
+++ b/SMP-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wunpe\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB375B2-D96D-4859-8F17-F94768F26F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96E898C-82E9-4314-A1CF-8914638E3F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9585" yWindow="0" windowWidth="19215" windowHeight="16200" xr2:uid="{62D27BF9-C9DF-4690-B6C5-3786047679B0}"/>
   </bookViews>
@@ -1825,33 +1825,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1877,6 +1850,33 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6899,29 +6899,29 @@
       <c r="B17" s="74">
         <v>0</v>
       </c>
-      <c r="C17" s="246"/>
-      <c r="D17" s="247"/>
-      <c r="E17" s="247"/>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="248"/>
+      <c r="C17" s="237"/>
+      <c r="D17" s="238"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="238"/>
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="239"/>
       <c r="J17" s="34"/>
       <c r="K17" s="50"/>
       <c r="L17" s="51"/>
-      <c r="M17" s="237"/>
-      <c r="N17" s="238"/>
-      <c r="O17" s="238"/>
-      <c r="P17" s="238"/>
-      <c r="Q17" s="238"/>
-      <c r="R17" s="238"/>
-      <c r="S17" s="238"/>
-      <c r="T17" s="238"/>
-      <c r="U17" s="238"/>
-      <c r="V17" s="238"/>
-      <c r="W17" s="238"/>
-      <c r="X17" s="238"/>
-      <c r="Y17" s="239"/>
+      <c r="M17" s="246"/>
+      <c r="N17" s="247"/>
+      <c r="O17" s="247"/>
+      <c r="P17" s="247"/>
+      <c r="Q17" s="247"/>
+      <c r="R17" s="247"/>
+      <c r="S17" s="247"/>
+      <c r="T17" s="247"/>
+      <c r="U17" s="247"/>
+      <c r="V17" s="247"/>
+      <c r="W17" s="247"/>
+      <c r="X17" s="247"/>
+      <c r="Y17" s="248"/>
       <c r="Z17" s="84"/>
       <c r="AA17" s="84"/>
       <c r="AB17" s="84"/>
@@ -6943,29 +6943,29 @@
     <row r="18" spans="1:52" ht="18" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="31"/>
-      <c r="C18" s="249"/>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250"/>
-      <c r="F18" s="250"/>
-      <c r="G18" s="250"/>
-      <c r="H18" s="250"/>
-      <c r="I18" s="251"/>
+      <c r="C18" s="240"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="242"/>
       <c r="J18" s="35"/>
       <c r="K18" s="51"/>
       <c r="L18" s="51"/>
-      <c r="M18" s="240"/>
-      <c r="N18" s="241"/>
-      <c r="O18" s="241"/>
-      <c r="P18" s="241"/>
-      <c r="Q18" s="241"/>
-      <c r="R18" s="241"/>
-      <c r="S18" s="241"/>
-      <c r="T18" s="241"/>
-      <c r="U18" s="241"/>
-      <c r="V18" s="241"/>
-      <c r="W18" s="241"/>
-      <c r="X18" s="241"/>
-      <c r="Y18" s="242"/>
+      <c r="M18" s="249"/>
+      <c r="N18" s="250"/>
+      <c r="O18" s="250"/>
+      <c r="P18" s="250"/>
+      <c r="Q18" s="250"/>
+      <c r="R18" s="250"/>
+      <c r="S18" s="250"/>
+      <c r="T18" s="250"/>
+      <c r="U18" s="250"/>
+      <c r="V18" s="250"/>
+      <c r="W18" s="250"/>
+      <c r="X18" s="250"/>
+      <c r="Y18" s="251"/>
       <c r="Z18" s="84"/>
       <c r="AA18" s="84"/>
       <c r="AB18" s="84"/>
@@ -6990,29 +6990,29 @@
     <row r="19" spans="1:52" ht="30" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="31"/>
-      <c r="C19" s="249"/>
-      <c r="D19" s="250"/>
-      <c r="E19" s="250"/>
-      <c r="F19" s="250"/>
-      <c r="G19" s="250"/>
-      <c r="H19" s="250"/>
-      <c r="I19" s="251"/>
+      <c r="C19" s="240"/>
+      <c r="D19" s="241"/>
+      <c r="E19" s="241"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="241"/>
+      <c r="H19" s="241"/>
+      <c r="I19" s="242"/>
       <c r="J19" s="35"/>
       <c r="K19" s="51"/>
       <c r="L19" s="51"/>
-      <c r="M19" s="240"/>
-      <c r="N19" s="241"/>
-      <c r="O19" s="241"/>
-      <c r="P19" s="241"/>
-      <c r="Q19" s="241"/>
-      <c r="R19" s="241"/>
-      <c r="S19" s="241"/>
-      <c r="T19" s="241"/>
-      <c r="U19" s="241"/>
-      <c r="V19" s="241"/>
-      <c r="W19" s="241"/>
-      <c r="X19" s="241"/>
-      <c r="Y19" s="242"/>
+      <c r="M19" s="249"/>
+      <c r="N19" s="250"/>
+      <c r="O19" s="250"/>
+      <c r="P19" s="250"/>
+      <c r="Q19" s="250"/>
+      <c r="R19" s="250"/>
+      <c r="S19" s="250"/>
+      <c r="T19" s="250"/>
+      <c r="U19" s="250"/>
+      <c r="V19" s="250"/>
+      <c r="W19" s="250"/>
+      <c r="X19" s="250"/>
+      <c r="Y19" s="251"/>
       <c r="Z19" s="84"/>
       <c r="AA19" s="84"/>
       <c r="AB19" s="84"/>
@@ -7034,29 +7034,29 @@
     <row r="20" spans="1:52" ht="40.700000000000003" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="31"/>
-      <c r="C20" s="249"/>
-      <c r="D20" s="250"/>
-      <c r="E20" s="250"/>
-      <c r="F20" s="250"/>
-      <c r="G20" s="250"/>
-      <c r="H20" s="250"/>
-      <c r="I20" s="251"/>
+      <c r="C20" s="240"/>
+      <c r="D20" s="241"/>
+      <c r="E20" s="241"/>
+      <c r="F20" s="241"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="241"/>
+      <c r="I20" s="242"/>
       <c r="J20" s="35"/>
       <c r="K20" s="51"/>
       <c r="L20" s="51"/>
-      <c r="M20" s="240"/>
-      <c r="N20" s="241"/>
-      <c r="O20" s="241"/>
-      <c r="P20" s="241"/>
-      <c r="Q20" s="241"/>
-      <c r="R20" s="241"/>
-      <c r="S20" s="241"/>
-      <c r="T20" s="241"/>
-      <c r="U20" s="241"/>
-      <c r="V20" s="241"/>
-      <c r="W20" s="241"/>
-      <c r="X20" s="241"/>
-      <c r="Y20" s="242"/>
+      <c r="M20" s="249"/>
+      <c r="N20" s="250"/>
+      <c r="O20" s="250"/>
+      <c r="P20" s="250"/>
+      <c r="Q20" s="250"/>
+      <c r="R20" s="250"/>
+      <c r="S20" s="250"/>
+      <c r="T20" s="250"/>
+      <c r="U20" s="250"/>
+      <c r="V20" s="250"/>
+      <c r="W20" s="250"/>
+      <c r="X20" s="250"/>
+      <c r="Y20" s="251"/>
       <c r="Z20" s="84"/>
       <c r="AA20" s="84"/>
       <c r="AB20" s="84"/>
@@ -7078,29 +7078,29 @@
     <row r="21" spans="1:52" ht="37.700000000000003" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="31"/>
-      <c r="C21" s="249"/>
-      <c r="D21" s="250"/>
-      <c r="E21" s="250"/>
-      <c r="F21" s="250"/>
-      <c r="G21" s="250"/>
-      <c r="H21" s="250"/>
-      <c r="I21" s="251"/>
+      <c r="C21" s="240"/>
+      <c r="D21" s="241"/>
+      <c r="E21" s="241"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="242"/>
       <c r="J21" s="35"/>
       <c r="K21" s="51"/>
       <c r="L21" s="51"/>
-      <c r="M21" s="240"/>
-      <c r="N21" s="241"/>
-      <c r="O21" s="241"/>
-      <c r="P21" s="241"/>
-      <c r="Q21" s="241"/>
-      <c r="R21" s="241"/>
-      <c r="S21" s="241"/>
-      <c r="T21" s="241"/>
-      <c r="U21" s="241"/>
-      <c r="V21" s="241"/>
-      <c r="W21" s="241"/>
-      <c r="X21" s="241"/>
-      <c r="Y21" s="242"/>
+      <c r="M21" s="249"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="250"/>
+      <c r="P21" s="250"/>
+      <c r="Q21" s="250"/>
+      <c r="R21" s="250"/>
+      <c r="S21" s="250"/>
+      <c r="T21" s="250"/>
+      <c r="U21" s="250"/>
+      <c r="V21" s="250"/>
+      <c r="W21" s="250"/>
+      <c r="X21" s="250"/>
+      <c r="Y21" s="251"/>
       <c r="Z21" s="84"/>
       <c r="AA21" s="84"/>
       <c r="AB21" s="84"/>
@@ -7122,29 +7122,29 @@
     <row r="22" spans="1:52" ht="38.450000000000003" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="31"/>
-      <c r="C22" s="252"/>
-      <c r="D22" s="253"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="253"/>
-      <c r="H22" s="253"/>
-      <c r="I22" s="254"/>
+      <c r="C22" s="243"/>
+      <c r="D22" s="244"/>
+      <c r="E22" s="244"/>
+      <c r="F22" s="244"/>
+      <c r="G22" s="244"/>
+      <c r="H22" s="244"/>
+      <c r="I22" s="245"/>
       <c r="J22" s="36"/>
       <c r="K22" s="51"/>
       <c r="L22" s="51"/>
-      <c r="M22" s="243"/>
-      <c r="N22" s="244"/>
-      <c r="O22" s="244"/>
-      <c r="P22" s="244"/>
-      <c r="Q22" s="244"/>
-      <c r="R22" s="244"/>
-      <c r="S22" s="244"/>
-      <c r="T22" s="244"/>
-      <c r="U22" s="244"/>
-      <c r="V22" s="244"/>
-      <c r="W22" s="244"/>
-      <c r="X22" s="244"/>
-      <c r="Y22" s="245"/>
+      <c r="M22" s="252"/>
+      <c r="N22" s="253"/>
+      <c r="O22" s="253"/>
+      <c r="P22" s="253"/>
+      <c r="Q22" s="253"/>
+      <c r="R22" s="253"/>
+      <c r="S22" s="253"/>
+      <c r="T22" s="253"/>
+      <c r="U22" s="253"/>
+      <c r="V22" s="253"/>
+      <c r="W22" s="253"/>
+      <c r="X22" s="253"/>
+      <c r="Y22" s="254"/>
       <c r="Z22" s="84"/>
       <c r="AA22" s="84"/>
       <c r="AB22" s="84"/>
@@ -12034,7 +12034,7 @@
   <protectedRanges>
     <protectedRange password="F0B1" sqref="B17:B124" name="Range2_1"/>
   </protectedRanges>
-  <mergeCells count="168">
+  <mergeCells count="169">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:M4"/>
     <mergeCell ref="N2:AP2"/>
@@ -12106,6 +12106,7 @@
     <mergeCell ref="C17:I22"/>
     <mergeCell ref="J17:J22"/>
     <mergeCell ref="K17:L22"/>
+    <mergeCell ref="M17:Y22"/>
     <mergeCell ref="Z17:AP22"/>
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="C35:I40"/>

--- a/SMP-Template.xlsx
+++ b/SMP-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wunpe\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6959CE9-BF16-4758-9E40-2DD61A3F17AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DC98DB-8044-4882-A486-4517CE599A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{62D27BF9-C9DF-4690-B6C5-3786047679B0}"/>
   </bookViews>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2512,13 +2490,13 @@
       <xdr:col>32</xdr:col>
       <xdr:colOff>36236</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>5178</xdr:rowOff>
+      <xdr:rowOff>48490</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>145830</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>165654</xdr:rowOff>
+      <xdr:rowOff>165653</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2541,8 +2519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11445529" y="6884920"/>
-          <a:ext cx="368426" cy="522840"/>
+          <a:off x="11431600" y="6927272"/>
+          <a:ext cx="365903" cy="477381"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2683,71 +2661,51 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>180110</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>20782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>93372</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>148937</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1C173DC-3E6A-D0A5-E477-763ACAAFC865}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10671465" y="6899564"/>
+          <a:ext cx="522862" cy="488373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5831,9 +5789,7 @@
       <c r="AA11" s="178"/>
       <c r="AB11" s="177"/>
       <c r="AC11" s="178"/>
-      <c r="AD11" s="177" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="AD11" s="177"/>
       <c r="AE11" s="183"/>
       <c r="AF11" s="178"/>
       <c r="AG11" s="177"/>
